--- a/sources/table_normalization/xlsx/economy-table11.xlsx
+++ b/sources/table_normalization/xlsx/economy-table11.xlsx
@@ -208,12 +208,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="4"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color indexed="16"/>
@@ -270,12 +264,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="4"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
@@ -285,6 +273,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="4"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="5">
@@ -344,10 +345,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -377,77 +378,77 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -467,15 +468,13 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Заголовок 1" xfId="2" builtinId="16"/>
@@ -1104,31 +1103,31 @@
       <c r="B6" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="52" t="s">
+      <c r="J6" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="51" t="s">
+      <c r="K6" s="54" t="s">
         <v>15</v>
       </c>
       <c r="L6" s="53" t="s">
@@ -3106,20 +3105,20 @@
       </c>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1">
-      <c r="A59" s="54" t="s">
+      <c r="A59" s="51" t="s">
         <v>35</v>
       </c>
       <c r="B59" s="55"/>
-      <c r="C59" s="56"/>
-      <c r="D59" s="57"/>
-      <c r="E59" s="56"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="57"/>
-      <c r="I59" s="56"/>
-      <c r="J59" s="57"/>
-      <c r="K59" s="56"/>
-      <c r="L59" s="57"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1">
       <c r="A60" s="17" t="s">
@@ -3303,9 +3302,9 @@
     <hyperlink ref="A2:B2" location="Contents!A1" display="Back to contents"/>
   </hyperlinks>
   <pageMargins left="0.196850393700787" right="0.196850393700787" top="0.196850393700787" bottom="0.196850393700787" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="26" orientation="portrait" horizontalDpi="300"/>
+  <pageSetup paperSize="9" scale="26" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>